--- a/data_lake/freight/Ningbo Container Freight Index.xlsx
+++ b/data_lake/freight/Ningbo Container Freight Index.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59489A3-46F7-40D5-AD0B-4DC8103F9BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{788ECFA3-3787-4AA3-AF9C-75F33A6FFC9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{788ECFA3-3787-4AA3-AF9C-75F33A6FFC9B}"/>
   </bookViews>
   <sheets>
     <sheet name="NCFI" sheetId="1" r:id="rId1"/>

--- a/data_lake/freight/Ningbo Container Freight Index.xlsx
+++ b/data_lake/freight/Ningbo Container Freight Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59489A3-46F7-40D5-AD0B-4DC8103F9BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A720A78-C977-4191-A05A-004577733214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{788ECFA3-3787-4AA3-AF9C-75F33A6FFC9B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{788ECFA3-3787-4AA3-AF9C-75F33A6FFC9B}"/>
   </bookViews>
   <sheets>
     <sheet name="NCFI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1079,6 +1079,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2354,6 +2357,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3629,6 +3635,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4904,6 +4913,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6179,6 +6191,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7453,6 +7468,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8731,6 +8749,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10008,6 +10029,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11285,6 +11309,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12562,6 +12589,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13839,6 +13869,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15115,6 +15148,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16394,6 +16430,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -17672,6 +17711,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18950,6 +18992,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -20228,6 +20273,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -21506,6 +21554,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -22784,6 +22835,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -24061,6 +24115,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -25338,6 +25395,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -26615,6 +26675,9 @@
                 <c:pt idx="203">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -27891,6 +27954,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -29621,7 +29687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8DC26B-2F57-414E-945B-0C6427027198}">
-  <dimension ref="A1:AA205"/>
+  <dimension ref="A1:AA206"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="5" bestFit="1" customWidth="1"/>
@@ -46052,6 +46118,20 @@
       </c>
       <c r="Z205" s="6">
         <v>1960.93</v>
+      </c>
+    </row>
+    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A206" s="5">
+        <v>46241</v>
+      </c>
+      <c r="B206" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C206" s="4">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Ningbo Container Freight Index.xlsx
+++ b/data_lake/freight/Ningbo Container Freight Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A720A78-C977-4191-A05A-004577733214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EE3259-5E42-41C0-AB45-B7D44D1DD984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{788ECFA3-3787-4AA3-AF9C-75F33A6FFC9B}"/>
   </bookViews>
@@ -1703,6 +1703,9 @@
                 <c:pt idx="203">
                   <c:v>2348.17</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2423.15</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2981,6 +2984,9 @@
                 <c:pt idx="203">
                   <c:v>2093.0100000000002</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2051.0700000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4259,6 +4265,9 @@
                 <c:pt idx="203">
                   <c:v>2414.5300000000002</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2269.56</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5537,6 +5546,9 @@
                 <c:pt idx="203">
                   <c:v>1872.62</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>1720.53</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6815,6 +6827,9 @@
                 <c:pt idx="203">
                   <c:v>3550.61</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>3836.86</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8092,6 +8107,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>3122.32</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3298.34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9373,6 +9391,9 @@
                 <c:pt idx="203">
                   <c:v>4795.84</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>5015.5200000000004</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10653,6 +10674,9 @@
                 <c:pt idx="203">
                   <c:v>1962.2</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2281.54</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11933,6 +11957,9 @@
                 <c:pt idx="203">
                   <c:v>3316.66</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>3551.43</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13213,6 +13240,9 @@
                 <c:pt idx="203">
                   <c:v>2632.15</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2922.72</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14493,6 +14523,9 @@
                 <c:pt idx="203">
                   <c:v>4447.9799999999996</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>4540.83</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15772,6 +15805,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>3146.18</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3115.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17054,6 +17090,9 @@
                 <c:pt idx="203">
                   <c:v>207.58</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>207.58</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -18335,6 +18374,9 @@
                 <c:pt idx="203">
                   <c:v>292.77</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>293.27999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -19616,6 +19658,9 @@
                 <c:pt idx="203">
                   <c:v>854.05</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>915.99</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -20897,6 +20942,9 @@
                 <c:pt idx="203">
                   <c:v>1636.41</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>1616.95</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -22178,6 +22226,9 @@
                 <c:pt idx="203">
                   <c:v>73.11</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>73.97</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -23459,6 +23510,9 @@
                 <c:pt idx="203">
                   <c:v>1931.91</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>1783.73</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -24739,6 +24793,9 @@
                 <c:pt idx="203">
                   <c:v>1430.15</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>1402.16</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -26019,6 +26076,9 @@
                 <c:pt idx="203">
                   <c:v>2153.69</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>2303.0100000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -27299,6 +27359,9 @@
                 <c:pt idx="203">
                   <c:v>1799.13</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>1815.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -28578,6 +28641,9 @@
                 </c:pt>
                 <c:pt idx="203">
                   <c:v>1960.93</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1924.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -46133,6 +46199,72 @@
       <c r="D206" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E206" s="6">
+        <v>2423.15</v>
+      </c>
+      <c r="F206" s="6">
+        <v>2051.0700000000002</v>
+      </c>
+      <c r="G206" s="6">
+        <v>2269.56</v>
+      </c>
+      <c r="H206" s="6">
+        <v>1720.53</v>
+      </c>
+      <c r="I206" s="6">
+        <v>3836.86</v>
+      </c>
+      <c r="J206" s="6">
+        <v>3298.34</v>
+      </c>
+      <c r="K206" s="6">
+        <v>5015.5200000000004</v>
+      </c>
+      <c r="L206" s="6">
+        <v>2281.54</v>
+      </c>
+      <c r="M206" s="6">
+        <v>3551.43</v>
+      </c>
+      <c r="N206" s="6">
+        <v>2922.72</v>
+      </c>
+      <c r="O206" s="6">
+        <v>4540.83</v>
+      </c>
+      <c r="P206" s="6">
+        <v>3115.68</v>
+      </c>
+      <c r="Q206" s="6">
+        <v>207.58</v>
+      </c>
+      <c r="R206" s="6">
+        <v>293.27999999999997</v>
+      </c>
+      <c r="S206" s="6">
+        <v>915.99</v>
+      </c>
+      <c r="T206" s="6">
+        <v>1616.95</v>
+      </c>
+      <c r="U206" s="6">
+        <v>73.97</v>
+      </c>
+      <c r="V206" s="6">
+        <v>1783.73</v>
+      </c>
+      <c r="W206" s="6">
+        <v>1402.16</v>
+      </c>
+      <c r="X206" s="6">
+        <v>2303.0100000000002</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>1815.55</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>1924.69</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA205">
@@ -46168,10 +46300,10 @@
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="7">
-        <v>44799</v>
+        <v>46241</v>
       </c>
       <c r="D3" s="7">
-        <v>44792</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -46179,13 +46311,13 @@
         <v>21</v>
       </c>
       <c r="C4" s="6">
-        <v>2400.27</v>
+        <v>2423.15</v>
       </c>
       <c r="D4" s="6">
-        <v>2588.08</v>
+        <v>2348.17</v>
       </c>
       <c r="E4" s="2">
-        <v>-7.2599999999999998E-2</v>
+        <v>3.1899999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -46193,13 +46325,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="6">
-        <v>3273.3</v>
+        <v>2051.0700000000002</v>
       </c>
       <c r="D5" s="6">
-        <v>3342.35</v>
+        <v>2093.0100000000002</v>
       </c>
       <c r="E5" s="2">
-        <v>-2.07E-2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -46207,13 +46339,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="6">
-        <v>3471.99</v>
+        <v>2269.56</v>
       </c>
       <c r="D6" s="6">
-        <v>3798.64</v>
+        <v>2414.5300000000002</v>
       </c>
       <c r="E6" s="2">
-        <v>-8.5999999999999993E-2</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -46221,13 +46353,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>2786.54</v>
+        <v>1720.53</v>
       </c>
       <c r="D7" s="6">
-        <v>3095.77</v>
+        <v>1872.62</v>
       </c>
       <c r="E7" s="2">
-        <v>-9.9900000000000003E-2</v>
+        <v>-8.1199999999999994E-2</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -46235,13 +46367,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="6">
-        <v>2682</v>
+        <v>3836.86</v>
       </c>
       <c r="D8" s="6">
-        <v>3119.35</v>
+        <v>3550.61</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.14019999999999999</v>
+        <v>8.0600000000000005E-2</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -46249,13 +46381,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="6">
-        <v>2944.8</v>
+        <v>3298.34</v>
       </c>
       <c r="D9" s="6">
-        <v>3078.26</v>
+        <v>3122.32</v>
       </c>
       <c r="E9" s="2">
-        <v>-4.3400000000000001E-2</v>
+        <v>5.6399999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -46263,13 +46395,13 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>1233.46</v>
+        <v>5015.5200000000004</v>
       </c>
       <c r="D10" s="6">
-        <v>1422.37</v>
+        <v>4795.84</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.1328</v>
+        <v>4.58E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -46277,13 +46409,13 @@
         <v>12</v>
       </c>
       <c r="C11" s="6">
-        <v>2224.4499999999998</v>
+        <v>2281.54</v>
       </c>
       <c r="D11" s="6">
-        <v>2340.7399999999998</v>
+        <v>1962.2</v>
       </c>
       <c r="E11" s="2">
-        <v>-4.9700000000000001E-2</v>
+        <v>0.16270000000000001</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -46291,13 +46423,13 @@
         <v>13</v>
       </c>
       <c r="C12" s="6">
-        <v>4896.6000000000004</v>
+        <v>3551.43</v>
       </c>
       <c r="D12" s="6">
-        <v>5133.99</v>
+        <v>3316.66</v>
       </c>
       <c r="E12" s="2">
-        <v>-4.6199999999999998E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -46305,13 +46437,13 @@
         <v>23</v>
       </c>
       <c r="C13" s="6">
-        <v>2148.44</v>
+        <v>2922.72</v>
       </c>
       <c r="D13" s="6">
-        <v>2663.76</v>
+        <v>2632.15</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.19350000000000001</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -46319,13 +46451,13 @@
         <v>14</v>
       </c>
       <c r="C14" s="6">
-        <v>2250.6799999999998</v>
+        <v>4540.83</v>
       </c>
       <c r="D14" s="6">
-        <v>2506.9899999999998</v>
+        <v>4447.9799999999996</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.1022</v>
+        <v>2.0899999999999998E-2</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -46333,13 +46465,13 @@
         <v>24</v>
       </c>
       <c r="C15" s="6">
-        <v>3997.48</v>
+        <v>3115.68</v>
       </c>
       <c r="D15" s="6">
-        <v>4408.43</v>
+        <v>3146.18</v>
       </c>
       <c r="E15" s="2">
-        <v>-9.3200000000000005E-2</v>
+        <v>-9.7000000000000003E-3</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -46347,13 +46479,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="6">
-        <v>835.52</v>
+        <v>207.58</v>
       </c>
       <c r="D16" s="6">
-        <v>847.06</v>
+        <v>207.58</v>
       </c>
       <c r="E16" s="2">
-        <v>-1.3599999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -46361,13 +46493,13 @@
         <v>16</v>
       </c>
       <c r="C17" s="6">
-        <v>782.51</v>
+        <v>293.27999999999997</v>
       </c>
       <c r="D17" s="6">
-        <v>802.09</v>
+        <v>292.77</v>
       </c>
       <c r="E17" s="2">
-        <v>-2.4400000000000002E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -46375,13 +46507,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="6">
-        <v>359.39</v>
+        <v>915.99</v>
       </c>
       <c r="D18" s="6">
-        <v>385.68</v>
+        <v>854.05</v>
       </c>
       <c r="E18" s="2">
-        <v>-6.8199999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -46389,13 +46521,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="6">
-        <v>1485.55</v>
+        <v>1616.95</v>
       </c>
       <c r="D19" s="6">
-        <v>1634.43</v>
+        <v>1636.41</v>
       </c>
       <c r="E19" s="2">
-        <v>-9.11E-2</v>
+        <v>-1.1900000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -46403,13 +46535,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="6">
-        <v>72.42</v>
+        <v>73.97</v>
       </c>
       <c r="D20" s="6">
-        <v>80.930000000000007</v>
+        <v>73.11</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.1051</v>
+        <v>1.18E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
@@ -46417,13 +46549,13 @@
         <v>28</v>
       </c>
       <c r="C21" s="6">
-        <v>2922.37</v>
+        <v>1783.73</v>
       </c>
       <c r="D21" s="6">
-        <v>3057.92</v>
+        <v>1931.91</v>
       </c>
       <c r="E21" s="2">
-        <v>-4.4299999999999999E-2</v>
+        <v>-7.6700000000000004E-2</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
@@ -46431,13 +46563,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="6">
-        <v>1803.35</v>
+        <v>1402.16</v>
       </c>
       <c r="D22" s="6">
-        <v>1920.65</v>
+        <v>1430.15</v>
       </c>
       <c r="E22" s="2">
-        <v>-6.1100000000000002E-2</v>
+        <v>-1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
@@ -46445,13 +46577,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="6">
-        <v>4381.57</v>
+        <v>2303.0100000000002</v>
       </c>
       <c r="D23" s="6">
-        <v>4406.66</v>
+        <v>2153.69</v>
       </c>
       <c r="E23" s="2">
-        <v>-5.7000000000000002E-3</v>
+        <v>6.93E-2</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
@@ -46459,13 +46591,13 @@
         <v>31</v>
       </c>
       <c r="C24" s="6">
-        <v>1645.28</v>
+        <v>1815.55</v>
       </c>
       <c r="D24" s="6">
-        <v>1723.8</v>
+        <v>1799.13</v>
       </c>
       <c r="E24" s="2">
-        <v>-4.5600000000000002E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -46473,13 +46605,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="6">
-        <v>3046.11</v>
+        <v>1924.69</v>
       </c>
       <c r="D25" s="6">
-        <v>3419.52</v>
+        <v>1960.93</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.10920000000000001</v>
+        <v>-1.8499999999999999E-2</v>
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.3">
